--- a/Copia de Matriz_Registro_de_Equipos_de_TI(1).xlsx
+++ b/Copia de Matriz_Registro_de_Equipos_de_TI(1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ELOSO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\estudiante\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1F05C07-7565-4B13-BD65-CA4C6ED3064C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D90A812-BF35-4CA8-9D87-4BFDA73C4AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -406,6 +406,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -436,7 +437,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -669,34 +669,34 @@
   <sheetData>
     <row r="1" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="23" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" spans="2:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="25" t="s">
+      <c r="C3" s="21"/>
+      <c r="D3" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="27"/>
     </row>
     <row r="4" spans="2:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="22"/>
+      <c r="C4" s="23"/>
       <c r="D4" s="5" t="s">
         <v>7</v>
       </c>
@@ -784,7 +784,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G8" s="15" t="s">
         <v>16</v>
@@ -861,7 +861,7 @@
       <c r="G13" s="11"/>
     </row>
     <row r="17" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G17" s="27"/>
+      <c r="G17" s="17"/>
     </row>
     <row r="19" spans="7:7" ht="14.25" x14ac:dyDescent="0.2"/>
     <row r="21" spans="7:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2"/>
